--- a/hplc and IR data/HPLC data for training/ac0091-5.xlsx
+++ b/hplc and IR data/HPLC data for training/ac0091-5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiayuzhang/Desktop/Hein lab/ChemoIR/BTM/HPLC data for training/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Heinlab\ChemoIR BTM\Data-driven-IR-calibration-model-investigations\hplc and IR data\HPLC data for training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200B7235-3F4F-CD4F-8276-5A3F982ABA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C035BA-F20A-4628-8EE9-312BAD25B200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="460" windowWidth="23680" windowHeight="15460" xr2:uid="{E7A7D5D2-32E5-4F4C-84D1-ECA5501B31F3}"/>
+    <workbookView xWindow="1080" yWindow="2205" windowWidth="21600" windowHeight="12630" xr2:uid="{E7A7D5D2-32E5-4F4C-84D1-ECA5501B31F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>DateTime</t>
   </si>
@@ -58,6 +61,9 @@
   </si>
   <si>
     <t>sum (M)</t>
+  </si>
+  <si>
+    <t>alcohol</t>
   </si>
 </sst>
 </file>
@@ -2000,14 +2006,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{816B798C-7BB5-4CC7-9F7D-0EF3539B2015}">
   <dimension ref="A1:K31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2025,7 +2031,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>5.849988425925926E-3</v>
       </c>
@@ -2057,7 +2063,7 @@
         <v>0.14515468560151806</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>6.4667129629629632E-3</v>
       </c>
@@ -2086,7 +2092,7 @@
         <v>0.14505398608741754</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1.1126759259259258E-2</v>
       </c>
@@ -2109,7 +2115,7 @@
         <v>0.14645784649752366</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1.5785902777777777E-2</v>
       </c>
@@ -2132,7 +2138,7 @@
         <v>0.14853616327822144</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2.0449097222222223E-2</v>
       </c>
@@ -2155,7 +2161,7 @@
         <v>0.14881247561510649</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2.5110787037037039E-2</v>
       </c>
@@ -2178,7 +2184,7 @@
         <v>0.15052152206242009</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2.9773229166666668E-2</v>
       </c>
@@ -2201,7 +2207,7 @@
         <v>0.15093943912267616</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>3.4442835648148144E-2</v>
       </c>
@@ -2224,7 +2230,7 @@
         <v>0.15036225314336554</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>3.9160312500000002E-2</v>
       </c>
@@ -2247,7 +2253,7 @@
         <v>0.15238682952284946</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>5.0765497685185186E-2</v>
       </c>
@@ -2270,7 +2276,7 @@
         <v>0.15373455553988846</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>6.2373090277777779E-2</v>
       </c>
@@ -2293,7 +2299,7 @@
         <v>0.1542333669033529</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>7.3985219907407418E-2</v>
       </c>
@@ -2316,7 +2322,7 @@
         <v>0.15436328341662969</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>8.5603298611111114E-2</v>
       </c>
@@ -2339,7 +2345,7 @@
         <v>0.15401441735676535</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>9.7216782407407415E-2</v>
       </c>
@@ -2362,7 +2368,7 @@
         <v>0.15484520930587112</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>0.10882288194444445</v>
       </c>
@@ -2385,7 +2391,7 @@
         <v>0.15508964483673465</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>0.12044327546296298</v>
       </c>
@@ -2408,7 +2414,7 @@
         <v>0.15490105079829736</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>0.13205684027777778</v>
       </c>
@@ -2431,7 +2437,7 @@
         <v>0.156097727004886</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>0.14367457175925927</v>
       </c>
@@ -2454,7 +2460,7 @@
         <v>0.15588524472779322</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>0.1552804976851852</v>
       </c>
@@ -2477,7 +2483,7 @@
         <v>0.15528070333063437</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>0.16689046296296295</v>
       </c>
@@ -2500,7 +2506,7 @@
         <v>0.15423037219413965</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>0.17850560185185185</v>
       </c>
@@ -2523,7 +2529,7 @@
         <v>0.15417603904003471</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>0.19011812499999997</v>
       </c>
@@ -2546,7 +2552,7 @@
         <v>0.15435464934962201</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>0.20172501157407408</v>
       </c>
@@ -2569,7 +2575,7 @@
         <v>0.15463752196133002</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>0.2133286921296296</v>
       </c>
@@ -2592,7 +2598,7 @@
         <v>0.15506569349259164</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>0.2249377662037037</v>
       </c>
@@ -2615,7 +2621,7 @@
         <v>0.15433261216859018</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>0.23654701388888888</v>
       </c>
@@ -2638,7 +2644,7 @@
         <v>0.15307275630056827</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>0.24816452546296297</v>
       </c>
@@ -2661,7 +2667,7 @@
         <v>0.15294728117478432</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>0.25977230324074074</v>
       </c>
@@ -2684,7 +2690,7 @@
         <v>0.15250511116648724</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>0.27137989583333333</v>
       </c>
@@ -2707,7 +2713,7 @@
         <v>0.15144751318514199</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>0.2829830439814815</v>
       </c>
